--- a/Data/EC/NIT-9008987631.xlsx
+++ b/Data/EC/NIT-9008987631.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A995F898-4A10-4BB5-AD57-30096508B8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D660BA93-7357-4094-B0B8-930AB8D30AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{29519163-D4E0-4D54-8AFD-E03A8D61A423}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5C016740-4461-4013-918D-B996E9EF8651}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -746,22 +746,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A11C0DBD-217F-BE6D-7B0E-F6B065513D74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F2430B-037E-A579-F5E5-D23915452498}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -770,7 +770,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -783,7 +783,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1112,23 +1112,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98270A4C-9ECB-46A2-9C24-5666C8A55541}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE72EC2-EB8C-4044-8160-171EDC6207B8}">
   <dimension ref="B2:J396"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1141,7 +1141,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1152,7 +1152,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1163,7 +1163,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1174,8 +1174,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>104</v>
       </c>
@@ -1190,8 +1190,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1206,8 +1206,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>105</v>
       </c>
@@ -1222,8 +1222,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>106</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1294,7 +1294,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1340,7 +1340,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1363,7 +1363,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1409,7 +1409,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1432,7 +1432,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1455,7 +1455,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1524,7 +1524,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1685,7 +1685,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1708,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1731,7 +1731,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1754,7 +1754,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1777,7 +1777,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1800,7 +1800,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1823,7 +1823,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1846,7 +1846,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1869,7 +1869,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1915,7 +1915,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1961,7 +1961,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1984,7 +1984,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2030,7 +2030,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2053,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2076,7 +2076,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2099,7 +2099,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2122,7 +2122,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2168,7 +2168,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2191,7 +2191,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2214,7 +2214,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2260,7 +2260,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2283,7 +2283,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2306,7 +2306,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2352,7 +2352,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2375,7 +2375,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2398,7 +2398,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2444,7 +2444,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2467,7 +2467,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2513,7 +2513,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2559,7 +2559,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2582,7 +2582,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2651,7 +2651,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2674,7 +2674,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2720,7 +2720,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2743,7 +2743,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2789,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2812,7 +2812,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2881,7 +2881,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2904,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2927,7 +2927,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2973,7 +2973,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2996,7 +2996,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3019,7 +3019,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3042,7 +3042,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3111,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3134,7 +3134,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3157,7 +3157,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3180,7 +3180,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3226,7 +3226,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3249,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3272,7 +3272,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3341,7 +3341,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3364,7 +3364,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3387,7 +3387,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3433,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3456,7 +3456,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3479,7 +3479,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3502,7 +3502,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3525,7 +3525,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3548,7 +3548,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3571,7 +3571,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3617,7 +3617,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3640,7 +3640,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3686,7 +3686,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3709,7 +3709,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3732,7 +3732,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3778,7 +3778,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3801,7 +3801,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3824,7 +3824,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3847,7 +3847,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3893,7 +3893,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3916,7 +3916,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3939,7 +3939,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3962,7 +3962,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3985,7 +3985,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -4008,7 +4008,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -4031,7 +4031,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -4054,7 +4054,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4077,7 +4077,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4146,7 +4146,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4169,7 +4169,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4192,7 +4192,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4215,7 +4215,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4238,7 +4238,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4261,7 +4261,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4284,7 +4284,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4307,7 +4307,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4330,7 +4330,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4353,7 +4353,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4376,7 +4376,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4399,7 +4399,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4422,7 +4422,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4445,7 +4445,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4468,7 +4468,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4491,7 +4491,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4537,7 +4537,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4560,7 +4560,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4606,7 +4606,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4675,7 +4675,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4698,7 +4698,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4744,7 +4744,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4767,7 +4767,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4790,7 +4790,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4859,7 +4859,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4882,7 +4882,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4928,7 +4928,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4951,7 +4951,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4974,7 +4974,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -4997,7 +4997,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -5020,7 +5020,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -5043,7 +5043,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -5066,7 +5066,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5089,7 +5089,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5135,7 +5135,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5158,7 +5158,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5181,7 +5181,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5296,7 +5296,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5319,7 +5319,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5342,7 +5342,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5411,7 +5411,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5434,7 +5434,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5503,7 +5503,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5526,7 +5526,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5549,7 +5549,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5572,7 +5572,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5595,7 +5595,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5618,7 +5618,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5641,7 +5641,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5664,7 +5664,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5687,7 +5687,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5710,7 +5710,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5733,7 +5733,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5779,7 +5779,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5802,7 +5802,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5825,7 +5825,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5848,7 +5848,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5894,7 +5894,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5917,7 +5917,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -5963,7 +5963,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -5986,7 +5986,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -6009,7 +6009,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -6032,7 +6032,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -6055,7 +6055,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -6078,7 +6078,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6101,7 +6101,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6124,7 +6124,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6147,7 +6147,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6193,7 +6193,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6216,7 +6216,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6239,7 +6239,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6262,7 +6262,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6285,7 +6285,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6308,7 +6308,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6331,7 +6331,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6354,7 +6354,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6377,7 +6377,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6400,7 +6400,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6423,7 +6423,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
@@ -6446,7 +6446,7 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
@@ -6469,7 +6469,7 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
@@ -6492,7 +6492,7 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
@@ -6515,7 +6515,7 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
@@ -6538,7 +6538,7 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="15" t="s">
         <v>8</v>
       </c>
@@ -6561,7 +6561,7 @@
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="15" t="s">
         <v>8</v>
       </c>
@@ -6584,7 +6584,7 @@
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" s="15" t="s">
         <v>8</v>
       </c>
@@ -6607,7 +6607,7 @@
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" s="15" t="s">
         <v>8</v>
       </c>
@@ -6630,7 +6630,7 @@
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" s="15" t="s">
         <v>8</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="15" t="s">
         <v>8</v>
       </c>
@@ -6676,7 +6676,7 @@
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="15" t="s">
         <v>8</v>
       </c>
@@ -6699,7 +6699,7 @@
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" s="15" t="s">
         <v>8</v>
       </c>
@@ -6722,7 +6722,7 @@
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" s="15" t="s">
         <v>8</v>
       </c>
@@ -6745,7 +6745,7 @@
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" s="15" t="s">
         <v>8</v>
       </c>
@@ -6768,7 +6768,7 @@
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" s="15" t="s">
         <v>8</v>
       </c>
@@ -6791,7 +6791,7 @@
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" s="15" t="s">
         <v>8</v>
       </c>
@@ -6814,7 +6814,7 @@
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" s="15" t="s">
         <v>8</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" s="15" t="s">
         <v>8</v>
       </c>
@@ -6860,7 +6860,7 @@
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" s="15" t="s">
         <v>8</v>
       </c>
@@ -6883,7 +6883,7 @@
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" s="15" t="s">
         <v>8</v>
       </c>
@@ -6906,7 +6906,7 @@
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" s="15" t="s">
         <v>8</v>
       </c>
@@ -6929,7 +6929,7 @@
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" s="15" t="s">
         <v>8</v>
       </c>
@@ -6952,7 +6952,7 @@
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" s="15" t="s">
         <v>8</v>
       </c>
@@ -6975,7 +6975,7 @@
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" s="15" t="s">
         <v>8</v>
       </c>
@@ -6998,7 +6998,7 @@
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" s="15" t="s">
         <v>8</v>
       </c>
@@ -7021,7 +7021,7 @@
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" s="15" t="s">
         <v>8</v>
       </c>
@@ -7044,7 +7044,7 @@
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" s="15" t="s">
         <v>8</v>
       </c>
@@ -7067,7 +7067,7 @@
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" s="15" t="s">
         <v>8</v>
       </c>
@@ -7090,7 +7090,7 @@
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" s="15" t="s">
         <v>8</v>
       </c>
@@ -7113,7 +7113,7 @@
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" s="15" t="s">
         <v>8</v>
       </c>
@@ -7136,7 +7136,7 @@
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" s="15" t="s">
         <v>8</v>
       </c>
@@ -7159,7 +7159,7 @@
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" s="15" t="s">
         <v>8</v>
       </c>
@@ -7182,7 +7182,7 @@
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" s="15" t="s">
         <v>8</v>
       </c>
@@ -7205,7 +7205,7 @@
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" s="15" t="s">
         <v>8</v>
       </c>
@@ -7228,7 +7228,7 @@
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" s="15" t="s">
         <v>8</v>
       </c>
@@ -7251,7 +7251,7 @@
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" s="15" t="s">
         <v>8</v>
       </c>
@@ -7274,7 +7274,7 @@
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" s="15" t="s">
         <v>8</v>
       </c>
@@ -7297,7 +7297,7 @@
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" s="15" t="s">
         <v>8</v>
       </c>
@@ -7320,7 +7320,7 @@
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" s="15" t="s">
         <v>8</v>
       </c>
@@ -7343,7 +7343,7 @@
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" s="15" t="s">
         <v>8</v>
       </c>
@@ -7366,7 +7366,7 @@
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" s="15" t="s">
         <v>8</v>
       </c>
@@ -7389,7 +7389,7 @@
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" s="15" t="s">
         <v>8</v>
       </c>
@@ -7412,7 +7412,7 @@
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" s="15" t="s">
         <v>8</v>
       </c>
@@ -7435,7 +7435,7 @@
       <c r="I283" s="19"/>
       <c r="J283" s="20"/>
     </row>
-    <row r="284" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B284" s="15" t="s">
         <v>8</v>
       </c>
@@ -7458,7 +7458,7 @@
       <c r="I284" s="19"/>
       <c r="J284" s="20"/>
     </row>
-    <row r="285" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B285" s="15" t="s">
         <v>8</v>
       </c>
@@ -7481,7 +7481,7 @@
       <c r="I285" s="19"/>
       <c r="J285" s="20"/>
     </row>
-    <row r="286" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B286" s="15" t="s">
         <v>8</v>
       </c>
@@ -7504,7 +7504,7 @@
       <c r="I286" s="19"/>
       <c r="J286" s="20"/>
     </row>
-    <row r="287" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B287" s="15" t="s">
         <v>8</v>
       </c>
@@ -7527,7 +7527,7 @@
       <c r="I287" s="19"/>
       <c r="J287" s="20"/>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" s="15" t="s">
         <v>8</v>
       </c>
@@ -7550,7 +7550,7 @@
       <c r="I288" s="19"/>
       <c r="J288" s="20"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B289" s="15" t="s">
         <v>8</v>
       </c>
@@ -7573,7 +7573,7 @@
       <c r="I289" s="19"/>
       <c r="J289" s="20"/>
     </row>
-    <row r="290" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B290" s="15" t="s">
         <v>8</v>
       </c>
@@ -7596,7 +7596,7 @@
       <c r="I290" s="19"/>
       <c r="J290" s="20"/>
     </row>
-    <row r="291" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B291" s="15" t="s">
         <v>8</v>
       </c>
@@ -7619,7 +7619,7 @@
       <c r="I291" s="19"/>
       <c r="J291" s="20"/>
     </row>
-    <row r="292" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B292" s="15" t="s">
         <v>8</v>
       </c>
@@ -7642,7 +7642,7 @@
       <c r="I292" s="19"/>
       <c r="J292" s="20"/>
     </row>
-    <row r="293" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B293" s="15" t="s">
         <v>8</v>
       </c>
@@ -7665,7 +7665,7 @@
       <c r="I293" s="19"/>
       <c r="J293" s="20"/>
     </row>
-    <row r="294" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B294" s="15" t="s">
         <v>8</v>
       </c>
@@ -7688,7 +7688,7 @@
       <c r="I294" s="19"/>
       <c r="J294" s="20"/>
     </row>
-    <row r="295" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B295" s="15" t="s">
         <v>8</v>
       </c>
@@ -7711,7 +7711,7 @@
       <c r="I295" s="19"/>
       <c r="J295" s="20"/>
     </row>
-    <row r="296" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B296" s="15" t="s">
         <v>8</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="I296" s="19"/>
       <c r="J296" s="20"/>
     </row>
-    <row r="297" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B297" s="15" t="s">
         <v>8</v>
       </c>
@@ -7757,7 +7757,7 @@
       <c r="I297" s="19"/>
       <c r="J297" s="20"/>
     </row>
-    <row r="298" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B298" s="15" t="s">
         <v>8</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="I298" s="19"/>
       <c r="J298" s="20"/>
     </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B299" s="15" t="s">
         <v>8</v>
       </c>
@@ -7803,7 +7803,7 @@
       <c r="I299" s="19"/>
       <c r="J299" s="20"/>
     </row>
-    <row r="300" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B300" s="15" t="s">
         <v>8</v>
       </c>
@@ -7826,7 +7826,7 @@
       <c r="I300" s="19"/>
       <c r="J300" s="20"/>
     </row>
-    <row r="301" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B301" s="15" t="s">
         <v>8</v>
       </c>
@@ -7849,7 +7849,7 @@
       <c r="I301" s="19"/>
       <c r="J301" s="20"/>
     </row>
-    <row r="302" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B302" s="15" t="s">
         <v>8</v>
       </c>
@@ -7872,7 +7872,7 @@
       <c r="I302" s="19"/>
       <c r="J302" s="20"/>
     </row>
-    <row r="303" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B303" s="15" t="s">
         <v>8</v>
       </c>
@@ -7895,7 +7895,7 @@
       <c r="I303" s="19"/>
       <c r="J303" s="20"/>
     </row>
-    <row r="304" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B304" s="15" t="s">
         <v>8</v>
       </c>
@@ -7918,7 +7918,7 @@
       <c r="I304" s="19"/>
       <c r="J304" s="20"/>
     </row>
-    <row r="305" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B305" s="15" t="s">
         <v>8</v>
       </c>
@@ -7941,7 +7941,7 @@
       <c r="I305" s="19"/>
       <c r="J305" s="20"/>
     </row>
-    <row r="306" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B306" s="15" t="s">
         <v>8</v>
       </c>
@@ -7964,7 +7964,7 @@
       <c r="I306" s="19"/>
       <c r="J306" s="20"/>
     </row>
-    <row r="307" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B307" s="15" t="s">
         <v>8</v>
       </c>
@@ -7987,7 +7987,7 @@
       <c r="I307" s="19"/>
       <c r="J307" s="20"/>
     </row>
-    <row r="308" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B308" s="15" t="s">
         <v>8</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="I308" s="19"/>
       <c r="J308" s="20"/>
     </row>
-    <row r="309" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B309" s="15" t="s">
         <v>8</v>
       </c>
@@ -8033,7 +8033,7 @@
       <c r="I309" s="19"/>
       <c r="J309" s="20"/>
     </row>
-    <row r="310" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B310" s="15" t="s">
         <v>8</v>
       </c>
@@ -8056,7 +8056,7 @@
       <c r="I310" s="19"/>
       <c r="J310" s="20"/>
     </row>
-    <row r="311" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B311" s="15" t="s">
         <v>8</v>
       </c>
@@ -8079,7 +8079,7 @@
       <c r="I311" s="19"/>
       <c r="J311" s="20"/>
     </row>
-    <row r="312" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B312" s="15" t="s">
         <v>8</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="I312" s="19"/>
       <c r="J312" s="20"/>
     </row>
-    <row r="313" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B313" s="15" t="s">
         <v>8</v>
       </c>
@@ -8125,7 +8125,7 @@
       <c r="I313" s="19"/>
       <c r="J313" s="20"/>
     </row>
-    <row r="314" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B314" s="15" t="s">
         <v>8</v>
       </c>
@@ -8148,7 +8148,7 @@
       <c r="I314" s="19"/>
       <c r="J314" s="20"/>
     </row>
-    <row r="315" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B315" s="15" t="s">
         <v>8</v>
       </c>
@@ -8171,7 +8171,7 @@
       <c r="I315" s="19"/>
       <c r="J315" s="20"/>
     </row>
-    <row r="316" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B316" s="15" t="s">
         <v>8</v>
       </c>
@@ -8194,7 +8194,7 @@
       <c r="I316" s="19"/>
       <c r="J316" s="20"/>
     </row>
-    <row r="317" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B317" s="15" t="s">
         <v>8</v>
       </c>
@@ -8217,7 +8217,7 @@
       <c r="I317" s="19"/>
       <c r="J317" s="20"/>
     </row>
-    <row r="318" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B318" s="15" t="s">
         <v>8</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="I318" s="19"/>
       <c r="J318" s="20"/>
     </row>
-    <row r="319" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B319" s="15" t="s">
         <v>8</v>
       </c>
@@ -8263,7 +8263,7 @@
       <c r="I319" s="19"/>
       <c r="J319" s="20"/>
     </row>
-    <row r="320" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B320" s="15" t="s">
         <v>8</v>
       </c>
@@ -8286,7 +8286,7 @@
       <c r="I320" s="19"/>
       <c r="J320" s="20"/>
     </row>
-    <row r="321" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B321" s="15" t="s">
         <v>8</v>
       </c>
@@ -8309,7 +8309,7 @@
       <c r="I321" s="19"/>
       <c r="J321" s="20"/>
     </row>
-    <row r="322" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B322" s="15" t="s">
         <v>8</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="I322" s="19"/>
       <c r="J322" s="20"/>
     </row>
-    <row r="323" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="323" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B323" s="15" t="s">
         <v>8</v>
       </c>
@@ -8355,7 +8355,7 @@
       <c r="I323" s="19"/>
       <c r="J323" s="20"/>
     </row>
-    <row r="324" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="324" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B324" s="15" t="s">
         <v>8</v>
       </c>
@@ -8378,7 +8378,7 @@
       <c r="I324" s="19"/>
       <c r="J324" s="20"/>
     </row>
-    <row r="325" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="325" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B325" s="15" t="s">
         <v>8</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="I325" s="19"/>
       <c r="J325" s="20"/>
     </row>
-    <row r="326" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="326" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B326" s="15" t="s">
         <v>8</v>
       </c>
@@ -8424,7 +8424,7 @@
       <c r="I326" s="19"/>
       <c r="J326" s="20"/>
     </row>
-    <row r="327" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="327" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B327" s="15" t="s">
         <v>8</v>
       </c>
@@ -8447,7 +8447,7 @@
       <c r="I327" s="19"/>
       <c r="J327" s="20"/>
     </row>
-    <row r="328" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B328" s="15" t="s">
         <v>8</v>
       </c>
@@ -8470,7 +8470,7 @@
       <c r="I328" s="19"/>
       <c r="J328" s="20"/>
     </row>
-    <row r="329" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="329" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B329" s="15" t="s">
         <v>8</v>
       </c>
@@ -8493,7 +8493,7 @@
       <c r="I329" s="19"/>
       <c r="J329" s="20"/>
     </row>
-    <row r="330" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B330" s="15" t="s">
         <v>8</v>
       </c>
@@ -8516,7 +8516,7 @@
       <c r="I330" s="19"/>
       <c r="J330" s="20"/>
     </row>
-    <row r="331" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="331" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B331" s="15" t="s">
         <v>8</v>
       </c>
@@ -8539,7 +8539,7 @@
       <c r="I331" s="19"/>
       <c r="J331" s="20"/>
     </row>
-    <row r="332" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="332" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B332" s="15" t="s">
         <v>8</v>
       </c>
@@ -8562,7 +8562,7 @@
       <c r="I332" s="19"/>
       <c r="J332" s="20"/>
     </row>
-    <row r="333" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B333" s="15" t="s">
         <v>8</v>
       </c>
@@ -8585,7 +8585,7 @@
       <c r="I333" s="19"/>
       <c r="J333" s="20"/>
     </row>
-    <row r="334" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="334" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B334" s="15" t="s">
         <v>8</v>
       </c>
@@ -8608,7 +8608,7 @@
       <c r="I334" s="19"/>
       <c r="J334" s="20"/>
     </row>
-    <row r="335" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="335" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B335" s="15" t="s">
         <v>8</v>
       </c>
@@ -8631,7 +8631,7 @@
       <c r="I335" s="19"/>
       <c r="J335" s="20"/>
     </row>
-    <row r="336" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="336" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B336" s="15" t="s">
         <v>8</v>
       </c>
@@ -8654,7 +8654,7 @@
       <c r="I336" s="19"/>
       <c r="J336" s="20"/>
     </row>
-    <row r="337" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="337" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B337" s="15" t="s">
         <v>8</v>
       </c>
@@ -8677,7 +8677,7 @@
       <c r="I337" s="19"/>
       <c r="J337" s="20"/>
     </row>
-    <row r="338" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="338" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B338" s="15" t="s">
         <v>8</v>
       </c>
@@ -8700,7 +8700,7 @@
       <c r="I338" s="19"/>
       <c r="J338" s="20"/>
     </row>
-    <row r="339" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="339" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B339" s="15" t="s">
         <v>8</v>
       </c>
@@ -8723,7 +8723,7 @@
       <c r="I339" s="19"/>
       <c r="J339" s="20"/>
     </row>
-    <row r="340" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B340" s="15" t="s">
         <v>8</v>
       </c>
@@ -8746,7 +8746,7 @@
       <c r="I340" s="19"/>
       <c r="J340" s="20"/>
     </row>
-    <row r="341" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="341" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B341" s="15" t="s">
         <v>8</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="I341" s="19"/>
       <c r="J341" s="20"/>
     </row>
-    <row r="342" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="342" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B342" s="15" t="s">
         <v>8</v>
       </c>
@@ -8792,7 +8792,7 @@
       <c r="I342" s="19"/>
       <c r="J342" s="20"/>
     </row>
-    <row r="343" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="343" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B343" s="15" t="s">
         <v>8</v>
       </c>
@@ -8815,7 +8815,7 @@
       <c r="I343" s="19"/>
       <c r="J343" s="20"/>
     </row>
-    <row r="344" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="344" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B344" s="15" t="s">
         <v>8</v>
       </c>
@@ -8838,7 +8838,7 @@
       <c r="I344" s="19"/>
       <c r="J344" s="20"/>
     </row>
-    <row r="345" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="345" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B345" s="15" t="s">
         <v>8</v>
       </c>
@@ -8861,7 +8861,7 @@
       <c r="I345" s="19"/>
       <c r="J345" s="20"/>
     </row>
-    <row r="346" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="346" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B346" s="15" t="s">
         <v>8</v>
       </c>
@@ -8884,7 +8884,7 @@
       <c r="I346" s="19"/>
       <c r="J346" s="20"/>
     </row>
-    <row r="347" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="347" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B347" s="15" t="s">
         <v>8</v>
       </c>
@@ -8907,7 +8907,7 @@
       <c r="I347" s="19"/>
       <c r="J347" s="20"/>
     </row>
-    <row r="348" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="348" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B348" s="15" t="s">
         <v>8</v>
       </c>
@@ -8930,7 +8930,7 @@
       <c r="I348" s="19"/>
       <c r="J348" s="20"/>
     </row>
-    <row r="349" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="349" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B349" s="15" t="s">
         <v>8</v>
       </c>
@@ -8953,7 +8953,7 @@
       <c r="I349" s="19"/>
       <c r="J349" s="20"/>
     </row>
-    <row r="350" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="350" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B350" s="15" t="s">
         <v>8</v>
       </c>
@@ -8976,7 +8976,7 @@
       <c r="I350" s="19"/>
       <c r="J350" s="20"/>
     </row>
-    <row r="351" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="351" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B351" s="15" t="s">
         <v>8</v>
       </c>
@@ -8999,7 +8999,7 @@
       <c r="I351" s="19"/>
       <c r="J351" s="20"/>
     </row>
-    <row r="352" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="352" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B352" s="15" t="s">
         <v>8</v>
       </c>
@@ -9022,7 +9022,7 @@
       <c r="I352" s="19"/>
       <c r="J352" s="20"/>
     </row>
-    <row r="353" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B353" s="15" t="s">
         <v>8</v>
       </c>
@@ -9045,7 +9045,7 @@
       <c r="I353" s="19"/>
       <c r="J353" s="20"/>
     </row>
-    <row r="354" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="354" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B354" s="15" t="s">
         <v>8</v>
       </c>
@@ -9068,7 +9068,7 @@
       <c r="I354" s="19"/>
       <c r="J354" s="20"/>
     </row>
-    <row r="355" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B355" s="15" t="s">
         <v>8</v>
       </c>
@@ -9091,7 +9091,7 @@
       <c r="I355" s="19"/>
       <c r="J355" s="20"/>
     </row>
-    <row r="356" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B356" s="15" t="s">
         <v>8</v>
       </c>
@@ -9114,7 +9114,7 @@
       <c r="I356" s="19"/>
       <c r="J356" s="20"/>
     </row>
-    <row r="357" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B357" s="15" t="s">
         <v>8</v>
       </c>
@@ -9137,7 +9137,7 @@
       <c r="I357" s="19"/>
       <c r="J357" s="20"/>
     </row>
-    <row r="358" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B358" s="15" t="s">
         <v>8</v>
       </c>
@@ -9160,7 +9160,7 @@
       <c r="I358" s="19"/>
       <c r="J358" s="20"/>
     </row>
-    <row r="359" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B359" s="15" t="s">
         <v>8</v>
       </c>
@@ -9183,7 +9183,7 @@
       <c r="I359" s="19"/>
       <c r="J359" s="20"/>
     </row>
-    <row r="360" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B360" s="15" t="s">
         <v>8</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="I360" s="19"/>
       <c r="J360" s="20"/>
     </row>
-    <row r="361" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B361" s="15" t="s">
         <v>8</v>
       </c>
@@ -9229,7 +9229,7 @@
       <c r="I361" s="19"/>
       <c r="J361" s="20"/>
     </row>
-    <row r="362" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B362" s="15" t="s">
         <v>8</v>
       </c>
@@ -9252,7 +9252,7 @@
       <c r="I362" s="19"/>
       <c r="J362" s="20"/>
     </row>
-    <row r="363" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B363" s="15" t="s">
         <v>8</v>
       </c>
@@ -9275,7 +9275,7 @@
       <c r="I363" s="19"/>
       <c r="J363" s="20"/>
     </row>
-    <row r="364" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B364" s="15" t="s">
         <v>8</v>
       </c>
@@ -9298,7 +9298,7 @@
       <c r="I364" s="19"/>
       <c r="J364" s="20"/>
     </row>
-    <row r="365" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B365" s="15" t="s">
         <v>8</v>
       </c>
@@ -9321,7 +9321,7 @@
       <c r="I365" s="19"/>
       <c r="J365" s="20"/>
     </row>
-    <row r="366" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B366" s="15" t="s">
         <v>8</v>
       </c>
@@ -9344,7 +9344,7 @@
       <c r="I366" s="19"/>
       <c r="J366" s="20"/>
     </row>
-    <row r="367" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B367" s="15" t="s">
         <v>8</v>
       </c>
@@ -9367,7 +9367,7 @@
       <c r="I367" s="19"/>
       <c r="J367" s="20"/>
     </row>
-    <row r="368" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B368" s="15" t="s">
         <v>8</v>
       </c>
@@ -9390,7 +9390,7 @@
       <c r="I368" s="19"/>
       <c r="J368" s="20"/>
     </row>
-    <row r="369" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B369" s="15" t="s">
         <v>8</v>
       </c>
@@ -9413,7 +9413,7 @@
       <c r="I369" s="19"/>
       <c r="J369" s="20"/>
     </row>
-    <row r="370" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B370" s="15" t="s">
         <v>100</v>
       </c>
@@ -9436,7 +9436,7 @@
       <c r="I370" s="19"/>
       <c r="J370" s="20"/>
     </row>
-    <row r="371" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B371" s="15" t="s">
         <v>100</v>
       </c>
@@ -9459,7 +9459,7 @@
       <c r="I371" s="19"/>
       <c r="J371" s="20"/>
     </row>
-    <row r="372" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B372" s="15" t="s">
         <v>100</v>
       </c>
@@ -9482,7 +9482,7 @@
       <c r="I372" s="19"/>
       <c r="J372" s="20"/>
     </row>
-    <row r="373" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B373" s="15" t="s">
         <v>100</v>
       </c>
@@ -9505,7 +9505,7 @@
       <c r="I373" s="19"/>
       <c r="J373" s="20"/>
     </row>
-    <row r="374" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B374" s="15" t="s">
         <v>100</v>
       </c>
@@ -9528,7 +9528,7 @@
       <c r="I374" s="19"/>
       <c r="J374" s="20"/>
     </row>
-    <row r="375" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B375" s="15" t="s">
         <v>100</v>
       </c>
@@ -9551,7 +9551,7 @@
       <c r="I375" s="19"/>
       <c r="J375" s="20"/>
     </row>
-    <row r="376" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B376" s="15" t="s">
         <v>100</v>
       </c>
@@ -9574,7 +9574,7 @@
       <c r="I376" s="19"/>
       <c r="J376" s="20"/>
     </row>
-    <row r="377" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B377" s="15" t="s">
         <v>100</v>
       </c>
@@ -9597,7 +9597,7 @@
       <c r="I377" s="19"/>
       <c r="J377" s="20"/>
     </row>
-    <row r="378" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="378" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B378" s="15" t="s">
         <v>100</v>
       </c>
@@ -9620,7 +9620,7 @@
       <c r="I378" s="19"/>
       <c r="J378" s="20"/>
     </row>
-    <row r="379" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="379" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B379" s="15" t="s">
         <v>100</v>
       </c>
@@ -9643,7 +9643,7 @@
       <c r="I379" s="19"/>
       <c r="J379" s="20"/>
     </row>
-    <row r="380" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="380" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B380" s="15" t="s">
         <v>100</v>
       </c>
@@ -9666,7 +9666,7 @@
       <c r="I380" s="19"/>
       <c r="J380" s="20"/>
     </row>
-    <row r="381" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="381" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B381" s="15" t="s">
         <v>100</v>
       </c>
@@ -9689,7 +9689,7 @@
       <c r="I381" s="19"/>
       <c r="J381" s="20"/>
     </row>
-    <row r="382" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="382" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B382" s="15" t="s">
         <v>100</v>
       </c>
@@ -9712,7 +9712,7 @@
       <c r="I382" s="19"/>
       <c r="J382" s="20"/>
     </row>
-    <row r="383" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="383" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B383" s="15" t="s">
         <v>100</v>
       </c>
@@ -9735,7 +9735,7 @@
       <c r="I383" s="19"/>
       <c r="J383" s="20"/>
     </row>
-    <row r="384" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="384" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B384" s="15" t="s">
         <v>100</v>
       </c>
@@ -9758,7 +9758,7 @@
       <c r="I384" s="19"/>
       <c r="J384" s="20"/>
     </row>
-    <row r="385" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="385" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B385" s="15" t="s">
         <v>100</v>
       </c>
@@ -9781,7 +9781,7 @@
       <c r="I385" s="19"/>
       <c r="J385" s="20"/>
     </row>
-    <row r="386" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="386" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B386" s="15" t="s">
         <v>100</v>
       </c>
@@ -9804,7 +9804,7 @@
       <c r="I386" s="19"/>
       <c r="J386" s="20"/>
     </row>
-    <row r="387" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="387" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B387" s="15" t="s">
         <v>100</v>
       </c>
@@ -9827,7 +9827,7 @@
       <c r="I387" s="19"/>
       <c r="J387" s="20"/>
     </row>
-    <row r="388" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="388" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B388" s="15" t="s">
         <v>100</v>
       </c>
@@ -9850,7 +9850,7 @@
       <c r="I388" s="19"/>
       <c r="J388" s="20"/>
     </row>
-    <row r="389" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="389" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B389" s="15" t="s">
         <v>100</v>
       </c>
@@ -9873,7 +9873,7 @@
       <c r="I389" s="19"/>
       <c r="J389" s="20"/>
     </row>
-    <row r="390" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="390" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B390" s="21" t="s">
         <v>100</v>
       </c>
@@ -9896,7 +9896,7 @@
       <c r="I390" s="25"/>
       <c r="J390" s="26"/>
     </row>
-    <row r="395" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="395" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B395" s="32" t="s">
         <v>112</v>
       </c>
@@ -9907,7 +9907,7 @@
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
     </row>
-    <row r="396" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="396" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B396" s="32" t="s">
         <v>111</v>
       </c>
